--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_41.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2520995.057303665</v>
+        <v>2514128.064355009</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900518</v>
+        <v>286.4107162900416</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900518</v>
+        <v>286.4107162900416</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>97.030640593115</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -787,13 +787,13 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>87.87773861910863</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>385</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>270.1099056835944</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>297.9271412701616</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>102.4466513351298</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>385</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>385</v>
+        <v>40.68118314271408</v>
       </c>
       <c r="V9" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1456,16 +1456,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>73.04152018756567</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1614,13 +1614,13 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G14" t="n">
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>244.9427694002283</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1854,7 +1854,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H17" t="n">
         <v>58.00965870352741</v>
@@ -1902,7 +1902,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>242.2818334606677</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>392.8251739264733</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -1975,7 +1975,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V18" t="n">
         <v>64.51066719152016</v>
@@ -2094,10 +2094,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I20" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2328,13 +2328,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
@@ -2452,7 +2452,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V24" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W24" t="n">
         <v>82.37314290982852</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U27" t="n">
         <v>50.21035976018675</v>
@@ -2698,7 +2698,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>122.4329129537</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2805,7 +2805,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U29" t="n">
         <v>299.2212965486107</v>
@@ -2875,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>49.39139276613435</v>
+        <v>122.4329129537</v>
       </c>
     </row>
     <row r="31">
@@ -3042,7 +3042,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T32" t="n">
         <v>236.6755817285639</v>
@@ -3106,16 +3106,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S33" t="n">
         <v>116.5639999646113</v>
@@ -3273,7 +3273,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F35" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
         <v>53.75737228701621</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>80.50967533902144</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="R42" t="n">
         <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>129.9010681051558</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4330,16 +4330,16 @@
         <v>30.8</v>
       </c>
       <c r="M2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="N2" t="n">
-        <v>777.6999999999999</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>348.1303297822864</v>
       </c>
       <c r="C3" t="n">
         <v>250.1195817084329</v>
@@ -4430,22 +4430,22 @@
         <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>706.6417123214865</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>706.4292277152372</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>691.7719881278431</v>
+        <v>400.8938473128077</v>
       </c>
       <c r="W3" t="n">
-        <v>659.071843774481</v>
+        <v>368.1937029594455</v>
       </c>
       <c r="X3" t="n">
-        <v>639.0084705973218</v>
+        <v>348.1303297822864</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>348.1303297822864</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>282.3059186249661</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="C4" t="n">
-        <v>282.3059186249661</v>
+        <v>194.0522609126089</v>
       </c>
       <c r="D4" t="n">
-        <v>282.3059186249661</v>
+        <v>307.371405037609</v>
       </c>
       <c r="E4" t="n">
-        <v>400.1348228363792</v>
+        <v>425.200309249022</v>
       </c>
       <c r="F4" t="n">
-        <v>524.4957954283146</v>
+        <v>549.5612818409576</v>
       </c>
       <c r="G4" t="n">
-        <v>677.9023613151999</v>
+        <v>702.9678477278428</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>872.4844328872404</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1093.617311823323</v>
       </c>
       <c r="J4" t="n">
         <v>1429.635566063132</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4518,13 +4518,13 @@
         <v>68.05025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>239.9411733538506</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="X4" t="n">
-        <v>282.3059186249661</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="Y4" t="n">
-        <v>282.3059186249661</v>
+        <v>68.05025509417312</v>
       </c>
     </row>
     <row r="5">
@@ -4552,25 +4552,25 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>411.9499999999999</v>
+        <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>793.0999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>793.1</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250.1195817084329</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>250.1195817084329</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>250.1195817084329</v>
+        <v>596.2530132457184</v>
       </c>
       <c r="E6" t="n">
         <v>250.1195817084329</v>
@@ -4673,16 +4673,16 @@
         <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>575.7213878082415</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>543.0212434548794</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>522.9578702777202</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>522.9578702777202</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1210.336612312233</v>
+        <v>442.247684463691</v>
       </c>
       <c r="C7" t="n">
-        <v>1336.338618130668</v>
+        <v>568.2496902821268</v>
       </c>
       <c r="D7" t="n">
-        <v>1336.338618130668</v>
+        <v>681.5688344071269</v>
       </c>
       <c r="E7" t="n">
-        <v>1336.338618130668</v>
+        <v>799.39773861854</v>
       </c>
       <c r="F7" t="n">
-        <v>1336.338618130668</v>
+        <v>923.7587112104754</v>
       </c>
       <c r="G7" t="n">
-        <v>1336.338618130668</v>
+        <v>1077.165277097361</v>
       </c>
       <c r="H7" t="n">
-        <v>1336.338618130668</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="I7" t="n">
-        <v>1336.338618130668</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>218.8756791588049</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U7" t="n">
-        <v>465.4268717970915</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V7" t="n">
-        <v>664.2482646830374</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="W7" t="n">
-        <v>836.1391829427148</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="X7" t="n">
-        <v>987.1699739669083</v>
+        <v>219.0810461183667</v>
       </c>
       <c r="Y7" t="n">
-        <v>1098.579274645941</v>
+        <v>330.4903467973989</v>
       </c>
     </row>
     <row r="8">
@@ -4801,19 +4801,19 @@
         <v>411.9499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>793.0999999999999</v>
+        <v>777.6999999999997</v>
       </c>
       <c r="M8" t="n">
-        <v>793.1</v>
+        <v>1158.85</v>
       </c>
       <c r="N8" t="n">
-        <v>793.1</v>
+        <v>1540</v>
       </c>
       <c r="O8" t="n">
-        <v>793.1</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134.2814659950806</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="C9" t="n">
-        <v>134.2814659950806</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="D9" t="n">
-        <v>134.2814659950806</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="E9" t="n">
-        <v>30.8</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>473.7545795777692</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>468.3426955196744</v>
       </c>
       <c r="U9" t="n">
-        <v>575.9338724144908</v>
+        <v>427.2505913351147</v>
       </c>
       <c r="V9" t="n">
-        <v>187.0449835256019</v>
+        <v>412.5933517477206</v>
       </c>
       <c r="W9" t="n">
-        <v>154.3448391722397</v>
+        <v>379.8932073943585</v>
       </c>
       <c r="X9" t="n">
-        <v>134.2814659950806</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="Y9" t="n">
-        <v>134.2814659950806</v>
+        <v>359.8298342171994</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>640.4349490892855</v>
+        <v>404.9974293695179</v>
       </c>
       <c r="C10" t="n">
-        <v>640.4349490892855</v>
+        <v>530.9994351879537</v>
       </c>
       <c r="D10" t="n">
-        <v>753.7540932142856</v>
+        <v>644.3185793129538</v>
       </c>
       <c r="E10" t="n">
-        <v>871.5829974256986</v>
+        <v>762.1474835243669</v>
       </c>
       <c r="F10" t="n">
-        <v>995.9439700176341</v>
+        <v>886.5084561163023</v>
       </c>
       <c r="G10" t="n">
-        <v>1149.350535904519</v>
+        <v>1039.915022003188</v>
       </c>
       <c r="H10" t="n">
-        <v>1318.867121063917</v>
+        <v>1209.431607162585</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>1209.431607162585</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
@@ -4986,19 +4986,19 @@
         <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>277.3511926382866</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>377.6468203987998</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>377.6468203987998</v>
+        <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>528.6776114229933</v>
+        <v>181.8307910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>528.6776114229933</v>
+        <v>293.2400917032258</v>
       </c>
     </row>
     <row r="11">
@@ -5035,19 +5035,19 @@
         <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L11" t="n">
-        <v>44.72</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M11" t="n">
-        <v>555.568828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N11" t="n">
-        <v>1108.978828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F12" t="n">
-        <v>108.0308712378206</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="H12" t="n">
-        <v>44.72</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="I12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5257,10 +5257,10 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
         <v>44.72</v>
@@ -5284,10 +5284,10 @@
         <v>1500.287941766591</v>
       </c>
       <c r="O14" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F15" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G15" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I15" t="n">
         <v>44.72</v>
@@ -5393,7 +5393,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
         <v>103.3156148520479</v>
@@ -5506,25 +5506,25 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>179.7320762183977</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>179.7320762183977</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L17" t="n">
-        <v>179.7320762183977</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M17" t="n">
-        <v>690.5809049473327</v>
+        <v>1129.18</v>
       </c>
       <c r="N17" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="O17" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5545,13 +5545,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>275.2516144816847</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>803.3593153922999</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S18" t="n">
-        <v>685.6179012866319</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T18" t="n">
-        <v>629.7009667234867</v>
+        <v>763.9167385504074</v>
       </c>
       <c r="U18" t="n">
-        <v>578.9834316121869</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V18" t="n">
-        <v>513.8211415197422</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W18" t="n">
-        <v>430.6159466613296</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>360.0475229791199</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>310.1572272557519</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5737,31 +5737,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M20" t="n">
-        <v>690.5809049473327</v>
+        <v>1129.18</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D21" t="n">
         <v>44.72</v>
@@ -5867,7 +5867,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C22" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D22" t="n">
         <v>1010.366979583462</v>
@@ -5931,22 +5931,22 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X22" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y22" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="23">
@@ -5971,10 +5971,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
@@ -5992,7 +5992,7 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O23" t="n">
         <v>1243.990904947333</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6223,19 +6223,19 @@
         <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>1542.849113037656</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M26" t="n">
-        <v>1542.849113037656</v>
+        <v>1682.59</v>
       </c>
       <c r="N26" t="n">
-        <v>2096.259113037656</v>
+        <v>2236</v>
       </c>
       <c r="O26" t="n">
-        <v>2096.259113037656</v>
+        <v>2236</v>
       </c>
       <c r="P26" t="n">
-        <v>2096.259113037656</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>398.9989442256527</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>433.9045569997199</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6405,22 +6405,22 @@
         <v>44.72</v>
       </c>
       <c r="T28" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U28" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X28" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y28" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
         <v>44.72</v>
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>436.0291130376557</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M29" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6484,22 +6484,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D30" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F30" t="n">
         <v>44.72</v>
@@ -6575,10 +6575,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.1485167851398</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="31">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
         <v>44.72</v>
@@ -6691,25 +6691,25 @@
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>44.72</v>
+        <v>575.7700000000002</v>
       </c>
       <c r="L32" t="n">
-        <v>44.72</v>
+        <v>1129.18</v>
       </c>
       <c r="M32" t="n">
-        <v>555.568828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="N32" t="n">
-        <v>1108.978828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6718,25 +6718,25 @@
         <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T32" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.7782575464261</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D33" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E33" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F33" t="n">
         <v>44.72</v>
@@ -6794,28 +6794,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="34">
@@ -6904,16 +6904,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
         <v>157.615990899539</v>
@@ -6928,19 +6928,19 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>64.92117127106515</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>618.3311712710652</v>
+        <v>575.7700000000002</v>
       </c>
       <c r="L35" t="n">
-        <v>1171.741171271065</v>
+        <v>1129.18</v>
       </c>
       <c r="M35" t="n">
+        <v>1129.18</v>
+      </c>
+      <c r="N35" t="n">
         <v>1682.59</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2236</v>
       </c>
       <c r="O35" t="n">
         <v>2236</v>
@@ -6952,28 +6952,28 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6992,13 +6992,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
         <v>44.72</v>
@@ -7062,16 +7062,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
         <v>1153.55685638681</v>
@@ -7128,10 +7128,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7168,28 +7168,28 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M38" t="n">
-        <v>946.8779417665908</v>
+        <v>1682.59</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
         <v>2085.68327354774</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>126.0429043828499</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
         <v>1010.366979583462</v>
@@ -7362,13 +7362,13 @@
         <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7402,22 +7402,22 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="L41" t="n">
-        <v>1542.849113037656</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M41" t="n">
-        <v>1542.849113037656</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N41" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P41" t="n">
         <v>1797.400904947332</v>
@@ -7502,28 +7502,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1136.841549130715</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>274.6072361907175</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
         <v>90.8376455473191</v>
@@ -7590,16 +7590,16 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
         <v>745.8791912947012</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7648,16 +7648,16 @@
         <v>1151.54</v>
       </c>
       <c r="M44" t="n">
-        <v>1151.54</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N44" t="n">
-        <v>1704.95</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7782,7 +7782,7 @@
         <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
         <v>1153.55685638681</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>913.7065720867618</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>862.2489580698352</v>
@@ -7985,7 +7985,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>439.6923140185369</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8444,22 +8444,22 @@
         <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>385</v>
+        <v>369.4444444444442</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423175</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698355</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
-        <v>369.7315044851258</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,10 +8678,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,10 +8690,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>136.6628946047192</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8927,13 +8927,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P14" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>171.4188408091284</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
@@ -9407,7 +9407,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9635,10 +9635,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O23" t="n">
-        <v>370.361973797064</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>559.2870600406815</v>
@@ -9866,10 +9866,10 @@
         <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
@@ -9881,7 +9881,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>313.9750954005603</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M29" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>206.6237041381304</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,22 +10571,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>55.44822975121676</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N38" t="n">
-        <v>777.3630622928068</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>327.370891705079</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11291,19 +11291,19 @@
         <v>559.0000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>163.6326220461452</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -26293,7 +26293,7 @@
         <v>1290861.46634091</v>
       </c>
       <c r="J2" t="n">
-        <v>1290861.466340909</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="K2" t="n">
         <v>1290861.46634091</v>
@@ -26308,10 +26308,10 @@
         <v>1290861.46634091</v>
       </c>
       <c r="O2" t="n">
+        <v>1290861.466340909</v>
+      </c>
+      <c r="P2" t="n">
         <v>1290861.46634091</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1290861.466340909</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527352.5986435077</v>
+        <v>525836.7429551921</v>
       </c>
       <c r="C6" t="n">
-        <v>664930.5787773222</v>
+        <v>663414.7230890066</v>
       </c>
       <c r="D6" t="n">
-        <v>666991.3506896383</v>
+        <v>665475.4950013222</v>
       </c>
       <c r="E6" t="n">
-        <v>343108.0631143748</v>
+        <v>341366.2133012671</v>
       </c>
       <c r="F6" t="n">
-        <v>686298.9584598792</v>
+        <v>684557.1086467715</v>
       </c>
       <c r="G6" t="n">
-        <v>688244.5349280647</v>
+        <v>686502.6851149569</v>
       </c>
       <c r="H6" t="n">
-        <v>690192.811745366</v>
+        <v>688450.9619322583</v>
       </c>
       <c r="I6" t="n">
-        <v>692143.8083887262</v>
+        <v>690401.9585756186</v>
       </c>
       <c r="J6" t="n">
-        <v>278577.5445903506</v>
+        <v>276835.6947772432</v>
       </c>
       <c r="K6" t="n">
-        <v>696054.0403425703</v>
+        <v>694312.1905294628</v>
       </c>
       <c r="L6" t="n">
-        <v>698013.3159028299</v>
+        <v>696271.4660897224</v>
       </c>
       <c r="M6" t="n">
-        <v>638727.3917988098</v>
+        <v>636985.5419857017</v>
       </c>
       <c r="N6" t="n">
-        <v>701940.2888336628</v>
+        <v>700198.439020555</v>
       </c>
       <c r="O6" t="n">
-        <v>423908.0280914006</v>
+        <v>422166.1782782926</v>
       </c>
       <c r="P6" t="n">
-        <v>705878.6309424104</v>
+        <v>704136.7811293033</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26993,16 +26993,16 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -27039,19 +27039,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -27082,7 +27082,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>174</v>
@@ -27091,7 +27091,7 @@
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -27115,7 +27115,7 @@
         <v>-0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>264.0692718524043</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27566,13 +27566,13 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>317.4800265984052</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>29.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,10 +27594,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>374.6813268559163</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27654,10 +27654,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>290.2363174211334</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27749,16 +27749,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114.4466509627322</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>50.01054562754103</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27809,7 +27809,7 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27834,25 +27834,25 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>331.5498960513034</v>
       </c>
       <c r="I7" t="n">
         <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
-        <v>240.9875163806871</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
         <v>288.520773801143</v>
@@ -27879,19 +27879,19 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27995,13 +27995,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>240.2254458867828</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28031,22 +28031,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>81.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>15.21035976018675</v>
+        <v>359.5291766174727</v>
       </c>
       <c r="V9" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28068,7 +28068,7 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28086,13 +28086,13 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J10" t="n">
+        <v>257.6971901495909</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="J10" t="n">
-        <v>35.26894883590776</v>
-      </c>
-      <c r="K10" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,10 +28122,10 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>300.4790251258255</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28235,16 +28235,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>263.0617733495849</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>144.0848657037829</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28393,13 +28393,13 @@
         <v>350</v>
       </c>
       <c r="F14" t="n">
+        <v>350</v>
+      </c>
+      <c r="G14" t="n">
+        <v>350</v>
+      </c>
+      <c r="H14" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="G14" t="n">
-        <v>350</v>
-      </c>
-      <c r="H14" t="n">
-        <v>350</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28472,16 +28472,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>259.1265669988554</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28529,7 +28529,7 @@
         <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">
@@ -28633,7 +28633,7 @@
         <v>350</v>
       </c>
       <c r="G17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H17" t="n">
         <v>350</v>
@@ -28681,7 +28681,7 @@
         <v>350</v>
       </c>
       <c r="W17" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X17" t="n">
         <v>350</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>154.448623365906</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28754,7 +28754,7 @@
         <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -28873,10 +28873,10 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I20" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -29003,7 +29003,7 @@
         <v>350</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22">
@@ -29019,55 +29019,55 @@
         <v>350</v>
       </c>
       <c r="D22" t="n">
+        <v>350</v>
+      </c>
+      <c r="E22" t="n">
+        <v>350</v>
+      </c>
+      <c r="F22" t="n">
+        <v>350</v>
+      </c>
+      <c r="G22" t="n">
+        <v>350</v>
+      </c>
+      <c r="H22" t="n">
+        <v>350</v>
+      </c>
+      <c r="I22" t="n">
+        <v>350</v>
+      </c>
+      <c r="J22" t="n">
+        <v>350</v>
+      </c>
+      <c r="K22" t="n">
+        <v>350</v>
+      </c>
+      <c r="L22" t="n">
+        <v>350</v>
+      </c>
+      <c r="M22" t="n">
+        <v>350</v>
+      </c>
+      <c r="N22" t="n">
+        <v>350</v>
+      </c>
+      <c r="O22" t="n">
+        <v>350</v>
+      </c>
+      <c r="P22" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>350</v>
+      </c>
+      <c r="R22" t="n">
+        <v>350</v>
+      </c>
+      <c r="S22" t="n">
+        <v>350</v>
+      </c>
+      <c r="T22" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E22" t="n">
-        <v>350</v>
-      </c>
-      <c r="F22" t="n">
-        <v>350</v>
-      </c>
-      <c r="G22" t="n">
-        <v>350</v>
-      </c>
-      <c r="H22" t="n">
-        <v>350</v>
-      </c>
-      <c r="I22" t="n">
-        <v>350</v>
-      </c>
-      <c r="J22" t="n">
-        <v>350</v>
-      </c>
-      <c r="K22" t="n">
-        <v>350</v>
-      </c>
-      <c r="L22" t="n">
-        <v>350</v>
-      </c>
-      <c r="M22" t="n">
-        <v>350</v>
-      </c>
-      <c r="N22" t="n">
-        <v>350</v>
-      </c>
-      <c r="O22" t="n">
-        <v>350</v>
-      </c>
-      <c r="P22" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>350</v>
-      </c>
-      <c r="R22" t="n">
-        <v>350</v>
-      </c>
-      <c r="S22" t="n">
-        <v>350</v>
-      </c>
-      <c r="T22" t="n">
-        <v>350</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29107,13 +29107,13 @@
         <v>350</v>
       </c>
       <c r="G23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H23" t="n">
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29180,7 +29180,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>262.1624218828912</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29189,7 +29189,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29219,7 +29219,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
@@ -29231,7 +29231,7 @@
         <v>350</v>
       </c>
       <c r="V24" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W24" t="n">
         <v>350</v>
@@ -29420,7 +29420,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>325.7395358750273</v>
@@ -29456,13 +29456,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U27" t="n">
         <v>350</v>
@@ -29477,7 +29477,7 @@
         <v>350</v>
       </c>
       <c r="Y27" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C28" t="n">
         <v>350</v>
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29584,7 +29584,7 @@
         <v>350</v>
       </c>
       <c r="H29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I29" t="n">
         <v>150.0811596826846</v>
@@ -29620,7 +29620,7 @@
         <v>350</v>
       </c>
       <c r="T29" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U29" t="n">
         <v>350</v>
@@ -29654,10 +29654,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>325.7395358750273</v>
@@ -29711,10 +29711,10 @@
         <v>350</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
     </row>
     <row r="31">
@@ -29821,7 +29821,7 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T32" t="n">
         <v>350</v>
@@ -29866,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="W32" t="n">
-        <v>350.0000000000001</v>
+        <v>350</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29885,16 +29885,16 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>325.7395358750273</v>
@@ -29930,7 +29930,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S33" t="n">
         <v>350</v>
@@ -30052,7 +30052,7 @@
         <v>350</v>
       </c>
       <c r="F35" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G35" t="n">
         <v>350</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30128,16 +30128,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>245.2298605360059</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
         <v>217.1263858913485</v>
@@ -30210,61 +30210,61 @@
         <v>350</v>
       </c>
       <c r="F37" t="n">
+        <v>350</v>
+      </c>
+      <c r="G37" t="n">
+        <v>350</v>
+      </c>
+      <c r="H37" t="n">
+        <v>350</v>
+      </c>
+      <c r="I37" t="n">
+        <v>350</v>
+      </c>
+      <c r="J37" t="n">
+        <v>350</v>
+      </c>
+      <c r="K37" t="n">
+        <v>350</v>
+      </c>
+      <c r="L37" t="n">
+        <v>350</v>
+      </c>
+      <c r="M37" t="n">
+        <v>350</v>
+      </c>
+      <c r="N37" t="n">
+        <v>350</v>
+      </c>
+      <c r="O37" t="n">
+        <v>350</v>
+      </c>
+      <c r="P37" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>350</v>
+      </c>
+      <c r="R37" t="n">
+        <v>350</v>
+      </c>
+      <c r="S37" t="n">
+        <v>350</v>
+      </c>
+      <c r="T37" t="n">
+        <v>350</v>
+      </c>
+      <c r="U37" t="n">
+        <v>350</v>
+      </c>
+      <c r="V37" t="n">
+        <v>350</v>
+      </c>
+      <c r="W37" t="n">
+        <v>350</v>
+      </c>
+      <c r="X37" t="n">
         <v>342.2113306341341</v>
-      </c>
-      <c r="G37" t="n">
-        <v>350</v>
-      </c>
-      <c r="H37" t="n">
-        <v>350</v>
-      </c>
-      <c r="I37" t="n">
-        <v>350</v>
-      </c>
-      <c r="J37" t="n">
-        <v>350</v>
-      </c>
-      <c r="K37" t="n">
-        <v>350</v>
-      </c>
-      <c r="L37" t="n">
-        <v>350</v>
-      </c>
-      <c r="M37" t="n">
-        <v>350</v>
-      </c>
-      <c r="N37" t="n">
-        <v>350</v>
-      </c>
-      <c r="O37" t="n">
-        <v>350</v>
-      </c>
-      <c r="P37" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>350</v>
-      </c>
-      <c r="R37" t="n">
-        <v>350</v>
-      </c>
-      <c r="S37" t="n">
-        <v>350</v>
-      </c>
-      <c r="T37" t="n">
-        <v>350</v>
-      </c>
-      <c r="U37" t="n">
-        <v>350</v>
-      </c>
-      <c r="V37" t="n">
-        <v>350</v>
-      </c>
-      <c r="W37" t="n">
-        <v>350</v>
-      </c>
-      <c r="X37" t="n">
-        <v>350</v>
       </c>
       <c r="Y37" t="n">
         <v>350</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30374,10 +30374,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>136.6167105523271</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30441,7 +30441,7 @@
         <v>350</v>
       </c>
       <c r="D40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="E40" t="n">
         <v>350</v>
@@ -30498,7 +30498,7 @@
         <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30638,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>173.0792650904796</v>
+        <v>110.4015025650371</v>
       </c>
       <c r="R42" t="n">
         <v>350</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30878,10 +30878,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -30918,10 +30918,10 @@
         <v>350</v>
       </c>
       <c r="E46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="F46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G46" t="n">
         <v>350</v>
@@ -34752,7 +34752,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>369.4444444444444</v>
+        <v>385</v>
       </c>
       <c r="N2" t="n">
         <v>385</v>
@@ -34764,7 +34764,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,10 +34880,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34901,7 +34901,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>339.4123780200084</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34940,10 +34940,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42.79267199102583</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,22 +34980,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35120,25 +35120,25 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>102.7787699496848</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>205.7185675447793</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35223,22 +35223,22 @@
         <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>385</v>
+        <v>369.4444444444442</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>385.0000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>385.0000000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>369.4444444444443</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35354,7 +35354,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35372,13 +35372,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>222.4282413136831</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,10 +35408,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>101.3087149096093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,10 +35469,10 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35706,13 +35706,13 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O17" t="n">
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>20.40522350612653</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
@@ -36186,7 +36186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36305,7 +36305,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D22" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E22" t="n">
         <v>69.01909516304346</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36414,10 +36414,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>300.1141042229716</v>
       </c>
       <c r="O23" t="n">
-        <v>300.1141042229716</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>559</v>
@@ -36645,10 +36645,10 @@
         <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
@@ -36660,7 +36660,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>141.1524110730749</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36773,7 +36773,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C28" t="n">
         <v>77.27475335195533</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M29" t="n">
-        <v>257.1230221309867</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>559</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,22 +37350,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>20.40522350612643</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37496,7 +37496,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G37" t="n">
         <v>104.95612715847</v>
@@ -37550,7 +37550,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y37" t="n">
         <v>62.53464715053764</v>
@@ -37590,25 +37590,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N38" t="n">
-        <v>300.1141042229716</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37727,7 +37727,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>69.01909516304346</v>
@@ -37784,7 +37784,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>93.38475247205324</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>559</v>
       </c>
-      <c r="L41" t="n">
+      <c r="O41" t="n">
         <v>559</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>257.1230221309866</v>
-      </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38070,19 +38070,19 @@
         <v>559.0000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>93.38475247205275</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38204,10 +38204,10 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>69.01909516304346</v>
+        <v>61.23042579717762</v>
       </c>
       <c r="F46" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G46" t="n">
         <v>104.95612715847</v>
